--- a/jogos_2025-06-30.xlsx
+++ b/jogos_2025-06-30.xlsx
@@ -232,24 +232,24 @@
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
     <t>Henan Jianye</t>
   </si>
   <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
@@ -271,12 +271,12 @@
     <t>Floresta</t>
   </si>
   <si>
+    <t>Colón</t>
+  </si>
+  <si>
     <t>Paysandu</t>
   </si>
   <si>
-    <t>Colón</t>
-  </si>
-  <si>
     <t>Itabaiana</t>
   </si>
   <si>
@@ -289,12 +289,12 @@
     <t>Shandong Luneng</t>
   </si>
   <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
@@ -316,10 +316,10 @@
     <t>Brusque</t>
   </si>
   <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
     <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
   </si>
   <si>
     <t>Botafogo PB</t>
@@ -1076,76 +1076,76 @@
         <v>105</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>2.55</v>
       </c>
       <c r="M3">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="N3">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="P3">
-        <v>18.5</v>
+        <v>14.25</v>
       </c>
       <c r="Q3">
-        <v>3.6</v>
+        <v>1.91</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V3">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="W3">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="Z3">
+        <v>1.18</v>
+      </c>
+      <c r="AA3">
+        <v>3.9</v>
+      </c>
+      <c r="AB3">
+        <v>1.7</v>
+      </c>
+      <c r="AC3">
+        <v>1.95</v>
+      </c>
+      <c r="AD3">
+        <v>2.75</v>
+      </c>
+      <c r="AE3">
+        <v>1.35</v>
+      </c>
+      <c r="AF3">
+        <v>1.62</v>
+      </c>
+      <c r="AG3">
+        <v>2.2</v>
+      </c>
+      <c r="AH3">
+        <v>5.2</v>
+      </c>
+      <c r="AI3">
         <v>1.1</v>
-      </c>
-      <c r="AA3">
-        <v>5.1</v>
-      </c>
-      <c r="AB3">
-        <v>1.48</v>
-      </c>
-      <c r="AC3">
-        <v>2.6</v>
-      </c>
-      <c r="AD3">
-        <v>1.95</v>
-      </c>
-      <c r="AE3">
-        <v>1.7</v>
-      </c>
-      <c r="AF3">
-        <v>1.67</v>
-      </c>
-      <c r="AG3">
-        <v>2.1</v>
-      </c>
-      <c r="AH3">
-        <v>3.5</v>
-      </c>
-      <c r="AI3">
-        <v>1.22</v>
       </c>
       <c r="AJ3" t="s">
         <v>106</v>
@@ -1154,13 +1154,13 @@
         <v>106</v>
       </c>
       <c r="AL3">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AM3">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AN3">
-        <v>2.86</v>
+        <v>1.49</v>
       </c>
       <c r="AO3">
         <v>-1</v>
@@ -1169,16 +1169,16 @@
         <v>1.25</v>
       </c>
       <c r="AQ3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AR3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AS3">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AT3">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AU3">
         <v>3.45</v>
@@ -1187,10 +1187,10 @@
         <v>2.55</v>
       </c>
       <c r="AW3">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AX3">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AY3">
         <v>1.41</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="BC3">
-        <v>3.6</v>
+        <v>1.91</v>
       </c>
       <c r="BD3" s="3">
         <v>45838.35763888889</v>
@@ -1246,76 +1246,76 @@
         <v>105</v>
       </c>
       <c r="L4">
-        <v>2.55</v>
+        <v>1.4</v>
       </c>
       <c r="M4">
+        <v>4.8</v>
+      </c>
+      <c r="N4">
+        <v>6.8</v>
+      </c>
+      <c r="O4">
+        <v>1.29</v>
+      </c>
+      <c r="P4">
+        <v>18.5</v>
+      </c>
+      <c r="Q4">
         <v>3.6</v>
       </c>
-      <c r="N4">
-        <v>2.5</v>
-      </c>
-      <c r="O4">
-        <v>1.91</v>
-      </c>
-      <c r="P4">
-        <v>14.25</v>
-      </c>
-      <c r="Q4">
-        <v>1.91</v>
-      </c>
       <c r="R4">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S4">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V4">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="Z4">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AA4">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="AB4">
+        <v>1.48</v>
+      </c>
+      <c r="AC4">
+        <v>2.6</v>
+      </c>
+      <c r="AD4">
+        <v>1.95</v>
+      </c>
+      <c r="AE4">
         <v>1.7</v>
       </c>
-      <c r="AC4">
-        <v>1.95</v>
-      </c>
-      <c r="AD4">
-        <v>2.75</v>
-      </c>
-      <c r="AE4">
-        <v>1.35</v>
-      </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH4">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="AI4">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="s">
         <v>106</v>
@@ -1324,13 +1324,13 @@
         <v>106</v>
       </c>
       <c r="AL4">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AM4">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AN4">
-        <v>1.49</v>
+        <v>2.86</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1339,16 +1339,16 @@
         <v>1.25</v>
       </c>
       <c r="AQ4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AR4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AS4">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AT4">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AU4">
         <v>3.45</v>
@@ -1357,10 +1357,10 @@
         <v>2.55</v>
       </c>
       <c r="AW4">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AX4">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AY4">
         <v>1.41</v>
@@ -1372,10 +1372,10 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="BC4">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="BD4" s="3">
         <v>45838.35763888889</v>
@@ -2606,76 +2606,76 @@
         <v>105</v>
       </c>
       <c r="L12">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="M12">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="N12">
-        <v>3.84</v>
+        <v>3.97</v>
       </c>
       <c r="O12">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="P12">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R12">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="S12">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="T12">
-        <v>3.58</v>
+        <v>4.8</v>
       </c>
       <c r="U12">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="V12">
         <v>11</v>
       </c>
       <c r="W12">
+        <v>1.02</v>
+      </c>
+      <c r="X12">
+        <v>1.15</v>
+      </c>
+      <c r="Y12">
+        <v>4.5</v>
+      </c>
+      <c r="Z12">
+        <v>1.76</v>
+      </c>
+      <c r="AA12">
+        <v>1.94</v>
+      </c>
+      <c r="AB12">
+        <v>3.25</v>
+      </c>
+      <c r="AC12">
+        <v>1.33</v>
+      </c>
+      <c r="AD12">
+        <v>6.75</v>
+      </c>
+      <c r="AE12">
+        <v>1.07</v>
+      </c>
+      <c r="AF12">
+        <v>2.5</v>
+      </c>
+      <c r="AG12">
+        <v>1.44</v>
+      </c>
+      <c r="AH12">
+        <v>15.5</v>
+      </c>
+      <c r="AI12">
         <v>1</v>
-      </c>
-      <c r="X12">
-        <v>1.09</v>
-      </c>
-      <c r="Y12">
-        <v>6</v>
-      </c>
-      <c r="Z12">
-        <v>1.48</v>
-      </c>
-      <c r="AA12">
-        <v>2.37</v>
-      </c>
-      <c r="AB12">
-        <v>2.39</v>
-      </c>
-      <c r="AC12">
-        <v>1.55</v>
-      </c>
-      <c r="AD12">
-        <v>5.15</v>
-      </c>
-      <c r="AE12">
-        <v>1.14</v>
-      </c>
-      <c r="AF12">
-        <v>2.15</v>
-      </c>
-      <c r="AG12">
-        <v>1.62</v>
-      </c>
-      <c r="AH12">
-        <v>10.5</v>
-      </c>
-      <c r="AI12">
-        <v>1.04</v>
       </c>
       <c r="AJ12" t="s">
         <v>106</v>
@@ -2684,46 +2684,46 @@
         <v>106</v>
       </c>
       <c r="AL12">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AM12">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AQ12">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AR12">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="AS12">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="AT12">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="AU12">
-        <v>3.55</v>
+        <v>2.23</v>
       </c>
       <c r="AV12">
-        <v>2.97</v>
+        <v>1.96</v>
       </c>
       <c r="AW12">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AX12">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="AY12">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -2732,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BC12">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="BD12" s="3">
         <v>45838.79166666666</v>
@@ -2776,76 +2776,76 @@
         <v>105</v>
       </c>
       <c r="L13">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="M13">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="N13">
-        <v>3.97</v>
+        <v>3.84</v>
       </c>
       <c r="O13">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q13">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R13">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="S13">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="T13">
-        <v>4.8</v>
+        <v>3.58</v>
       </c>
       <c r="U13">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V13">
         <v>11</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Y13">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="AA13">
-        <v>1.94</v>
+        <v>2.37</v>
       </c>
       <c r="AB13">
-        <v>3.25</v>
+        <v>2.39</v>
       </c>
       <c r="AC13">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AD13">
-        <v>6.75</v>
+        <v>5.15</v>
       </c>
       <c r="AE13">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AG13">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AH13">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AI13">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AJ13" t="s">
         <v>106</v>
@@ -2854,46 +2854,46 @@
         <v>106</v>
       </c>
       <c r="AL13">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN13">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="AQ13">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AR13">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="AS13">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="AT13">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="AU13">
-        <v>2.23</v>
+        <v>3.55</v>
       </c>
       <c r="AV13">
-        <v>1.96</v>
+        <v>2.97</v>
       </c>
       <c r="AW13">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AX13">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AY13">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -2902,10 +2902,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BC13">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="BD13" s="3">
         <v>45838.79166666666</v>
@@ -3089,7 +3089,7 @@
         <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>74</v>

--- a/jogos_2025-06-30.xlsx
+++ b/jogos_2025-06-30.xlsx
@@ -220,24 +220,24 @@
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
@@ -256,12 +256,12 @@
     <t>AGMK</t>
   </si>
   <si>
+    <t>Brann</t>
+  </si>
+  <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Brann</t>
-  </si>
-  <si>
     <t>Mjällby</t>
   </si>
   <si>
@@ -271,12 +271,12 @@
     <t>Floresta</t>
   </si>
   <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
     <t>Colón</t>
   </si>
   <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
     <t>Itabaiana</t>
   </si>
   <si>
@@ -301,12 +301,12 @@
     <t>Termez Surkhon</t>
   </si>
   <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
     <t>Norrköping</t>
   </si>
   <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
     <t>Malmö FF</t>
   </si>
   <si>
@@ -316,10 +316,10 @@
     <t>Brusque</t>
   </si>
   <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
     <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
   </si>
   <si>
     <t>Botafogo PB</t>
@@ -906,13 +906,13 @@
         <v>105</v>
       </c>
       <c r="L2">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="M2">
-        <v>3.9</v>
+        <v>3.83</v>
       </c>
       <c r="N2">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="O2">
         <v>2</v>
@@ -954,10 +954,10 @@
         <v>6.15</v>
       </c>
       <c r="AB2">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC2">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD2">
         <v>2.05</v>
@@ -1076,13 +1076,13 @@
         <v>105</v>
       </c>
       <c r="L3">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="M3">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N3">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O3">
         <v>1.91</v>
@@ -1246,13 +1246,13 @@
         <v>105</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="O4">
         <v>1.29</v>
@@ -1294,10 +1294,10 @@
         <v>5.1</v>
       </c>
       <c r="AB4">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AC4">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AD4">
         <v>1.95</v>
@@ -1586,13 +1586,13 @@
         <v>105</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1604,58 +1604,58 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ6" t="s">
         <v>106</v>
@@ -1664,13 +1664,13 @@
         <v>106</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AM6">
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AO6">
         <v>-1</v>
@@ -1756,76 +1756,76 @@
         <v>105</v>
       </c>
       <c r="L7">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="M7">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N7">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="Q7">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S7">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T7">
+        <v>2.1</v>
+      </c>
+      <c r="U7">
+        <v>1.67</v>
+      </c>
+      <c r="V7">
+        <v>4.5</v>
+      </c>
+      <c r="W7">
+        <v>1.18</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>17</v>
+      </c>
+      <c r="Z7">
+        <v>1.13</v>
+      </c>
+      <c r="AA7">
+        <v>5.75</v>
+      </c>
+      <c r="AB7">
+        <v>1.41</v>
+      </c>
+      <c r="AC7">
+        <v>2.78</v>
+      </c>
+      <c r="AD7">
+        <v>2.01</v>
+      </c>
+      <c r="AE7">
+        <v>1.71</v>
+      </c>
+      <c r="AF7">
+        <v>1.53</v>
+      </c>
+      <c r="AG7">
         <v>2.38</v>
       </c>
-      <c r="U7">
-        <v>1.53</v>
-      </c>
-      <c r="V7">
-        <v>6</v>
-      </c>
-      <c r="W7">
-        <v>1.13</v>
-      </c>
-      <c r="X7">
-        <v>1.04</v>
-      </c>
-      <c r="Y7">
-        <v>11</v>
-      </c>
-      <c r="Z7">
-        <v>1.22</v>
-      </c>
-      <c r="AA7">
-        <v>4.33</v>
-      </c>
-      <c r="AB7">
-        <v>1.65</v>
-      </c>
-      <c r="AC7">
-        <v>2.05</v>
-      </c>
-      <c r="AD7">
-        <v>2.27</v>
-      </c>
-      <c r="AE7">
-        <v>1.56</v>
-      </c>
-      <c r="AF7">
-        <v>1.67</v>
-      </c>
-      <c r="AG7">
-        <v>2.1</v>
-      </c>
       <c r="AH7">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="AI7">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AJ7" t="s">
         <v>106</v>
@@ -1834,46 +1834,46 @@
         <v>106</v>
       </c>
       <c r="AL7">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AM7">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AN7">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AO7">
         <v>-1</v>
       </c>
       <c r="AP7">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AQ7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AS7">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AT7">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AU7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AV7">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AW7">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AX7">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AY7">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -1882,10 +1882,10 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="BC7">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="BD7" s="3">
         <v>45838.58333333334</v>
@@ -1926,76 +1926,76 @@
         <v>105</v>
       </c>
       <c r="L8">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="M8">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="N8">
+        <v>4.1</v>
+      </c>
+      <c r="O8">
+        <v>1.44</v>
+      </c>
+      <c r="P8">
+        <v>11.5</v>
+      </c>
+      <c r="Q8">
+        <v>2.75</v>
+      </c>
+      <c r="R8">
+        <v>1.3</v>
+      </c>
+      <c r="S8">
+        <v>3.4</v>
+      </c>
+      <c r="T8">
+        <v>2.38</v>
+      </c>
+      <c r="U8">
+        <v>1.53</v>
+      </c>
+      <c r="V8">
+        <v>6</v>
+      </c>
+      <c r="W8">
+        <v>1.13</v>
+      </c>
+      <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>11</v>
+      </c>
+      <c r="Z8">
+        <v>1.22</v>
+      </c>
+      <c r="AA8">
+        <v>4.33</v>
+      </c>
+      <c r="AB8">
+        <v>1.65</v>
+      </c>
+      <c r="AC8">
+        <v>2.05</v>
+      </c>
+      <c r="AD8">
+        <v>2.27</v>
+      </c>
+      <c r="AE8">
+        <v>1.56</v>
+      </c>
+      <c r="AF8">
+        <v>1.67</v>
+      </c>
+      <c r="AG8">
+        <v>2.1</v>
+      </c>
+      <c r="AH8">
         <v>5</v>
       </c>
-      <c r="O8">
-        <v>1.36</v>
-      </c>
-      <c r="P8">
-        <v>16</v>
-      </c>
-      <c r="Q8">
-        <v>3</v>
-      </c>
-      <c r="R8">
-        <v>1.22</v>
-      </c>
-      <c r="S8">
-        <v>4</v>
-      </c>
-      <c r="T8">
-        <v>2.1</v>
-      </c>
-      <c r="U8">
-        <v>1.67</v>
-      </c>
-      <c r="V8">
-        <v>4.5</v>
-      </c>
-      <c r="W8">
+      <c r="AI8">
         <v>1.18</v>
-      </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
-        <v>17</v>
-      </c>
-      <c r="Z8">
-        <v>1.13</v>
-      </c>
-      <c r="AA8">
-        <v>5.75</v>
-      </c>
-      <c r="AB8">
-        <v>1.5</v>
-      </c>
-      <c r="AC8">
-        <v>2.4</v>
-      </c>
-      <c r="AD8">
-        <v>2.01</v>
-      </c>
-      <c r="AE8">
-        <v>1.71</v>
-      </c>
-      <c r="AF8">
-        <v>1.53</v>
-      </c>
-      <c r="AG8">
-        <v>2.38</v>
-      </c>
-      <c r="AH8">
-        <v>3.55</v>
-      </c>
-      <c r="AI8">
-        <v>1.28</v>
       </c>
       <c r="AJ8" t="s">
         <v>106</v>
@@ -2004,46 +2004,46 @@
         <v>106</v>
       </c>
       <c r="AL8">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AM8">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AN8">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AO8">
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ8">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR8">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AS8">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AT8">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AU8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV8">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AW8">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AX8">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AY8">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="BC8">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BD8" s="3">
         <v>45838.58333333334</v>
@@ -2069,7 +2069,7 @@
         <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
         <v>74</v>
@@ -2266,40 +2266,40 @@
         <v>105</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
         <v>0</v>
@@ -2308,34 +2308,34 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ10" t="s">
         <v>106</v>
@@ -2344,13 +2344,13 @@
         <v>106</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AM10">
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AO10">
         <v>-1</v>
@@ -2392,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BD10" s="3">
         <v>45838.66666666666</v>
@@ -2436,13 +2436,13 @@
         <v>105</v>
       </c>
       <c r="L11">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="M11">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="N11">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="O11">
         <v>2</v>
@@ -2454,31 +2454,31 @@
         <v>2.4</v>
       </c>
       <c r="R11">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="S11">
         <v>2.05</v>
       </c>
       <c r="T11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U11">
         <v>1.2</v>
       </c>
       <c r="V11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y11">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="Z11">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA11">
         <v>2.1</v>
@@ -2490,22 +2490,22 @@
         <v>1.5</v>
       </c>
       <c r="AD11">
-        <v>6.35</v>
+        <v>5.8</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG11">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AH11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI11">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AJ11" t="s">
         <v>106</v>
@@ -2514,7 +2514,7 @@
         <v>106</v>
       </c>
       <c r="AL11">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AM11">
         <v>1.43</v>
@@ -2529,31 +2529,31 @@
         <v>1.16</v>
       </c>
       <c r="AQ11">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AR11">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AS11">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="AT11">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AU11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV11">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="AW11">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="AX11">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AY11">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2606,76 +2606,76 @@
         <v>105</v>
       </c>
       <c r="L12">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="M12">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="N12">
-        <v>3.97</v>
+        <v>3.84</v>
       </c>
       <c r="O12">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q12">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R12">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="S12">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="T12">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="U12">
+        <v>1.27</v>
+      </c>
+      <c r="V12">
+        <v>10.5</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>1.09</v>
+      </c>
+      <c r="Y12">
+        <v>6</v>
+      </c>
+      <c r="Z12">
+        <v>1.48</v>
+      </c>
+      <c r="AA12">
+        <v>2.37</v>
+      </c>
+      <c r="AB12">
+        <v>2.39</v>
+      </c>
+      <c r="AC12">
+        <v>1.55</v>
+      </c>
+      <c r="AD12">
+        <v>5.6</v>
+      </c>
+      <c r="AE12">
         <v>1.17</v>
       </c>
-      <c r="V12">
-        <v>11</v>
-      </c>
-      <c r="W12">
-        <v>1.02</v>
-      </c>
-      <c r="X12">
-        <v>1.15</v>
-      </c>
-      <c r="Y12">
-        <v>4.5</v>
-      </c>
-      <c r="Z12">
-        <v>1.76</v>
-      </c>
-      <c r="AA12">
-        <v>1.94</v>
-      </c>
-      <c r="AB12">
-        <v>3.25</v>
-      </c>
-      <c r="AC12">
-        <v>1.33</v>
-      </c>
-      <c r="AD12">
-        <v>6.75</v>
-      </c>
-      <c r="AE12">
-        <v>1.07</v>
-      </c>
       <c r="AF12">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG12">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AH12">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="AI12">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AJ12" t="s">
         <v>106</v>
@@ -2684,46 +2684,46 @@
         <v>106</v>
       </c>
       <c r="AL12">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN12">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12">
-        <v>1.8</v>
+        <v>1.34</v>
       </c>
       <c r="AR12">
-        <v>2.21</v>
+        <v>1.6</v>
       </c>
       <c r="AS12">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="AT12">
-        <v>4.4</v>
+        <v>2.37</v>
       </c>
       <c r="AU12">
-        <v>2.23</v>
+        <v>4.1</v>
       </c>
       <c r="AV12">
-        <v>1.96</v>
+        <v>2.97</v>
       </c>
       <c r="AW12">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AX12">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AY12">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -2732,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BC12">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="BD12" s="3">
         <v>45838.79166666666</v>
@@ -2776,76 +2776,76 @@
         <v>105</v>
       </c>
       <c r="L13">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="M13">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="N13">
-        <v>3.84</v>
+        <v>3.97</v>
       </c>
       <c r="O13">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="P13">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="S13">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="T13">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="V13">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="W13">
+        <v>1.02</v>
+      </c>
+      <c r="X13">
+        <v>1.13</v>
+      </c>
+      <c r="Y13">
+        <v>4.4</v>
+      </c>
+      <c r="Z13">
+        <v>1.76</v>
+      </c>
+      <c r="AA13">
+        <v>1.94</v>
+      </c>
+      <c r="AB13">
+        <v>3.21</v>
+      </c>
+      <c r="AC13">
+        <v>1.3</v>
+      </c>
+      <c r="AD13">
+        <v>6.5</v>
+      </c>
+      <c r="AE13">
+        <v>1.1</v>
+      </c>
+      <c r="AF13">
+        <v>2.63</v>
+      </c>
+      <c r="AG13">
+        <v>1.44</v>
+      </c>
+      <c r="AH13">
+        <v>12</v>
+      </c>
+      <c r="AI13">
         <v>1</v>
-      </c>
-      <c r="X13">
-        <v>1.09</v>
-      </c>
-      <c r="Y13">
-        <v>6</v>
-      </c>
-      <c r="Z13">
-        <v>1.48</v>
-      </c>
-      <c r="AA13">
-        <v>2.37</v>
-      </c>
-      <c r="AB13">
-        <v>2.39</v>
-      </c>
-      <c r="AC13">
-        <v>1.55</v>
-      </c>
-      <c r="AD13">
-        <v>5.15</v>
-      </c>
-      <c r="AE13">
-        <v>1.14</v>
-      </c>
-      <c r="AF13">
-        <v>2.15</v>
-      </c>
-      <c r="AG13">
-        <v>1.62</v>
-      </c>
-      <c r="AH13">
-        <v>10.5</v>
-      </c>
-      <c r="AI13">
-        <v>1.04</v>
       </c>
       <c r="AJ13" t="s">
         <v>106</v>
@@ -2854,46 +2854,46 @@
         <v>106</v>
       </c>
       <c r="AL13">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AM13">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AQ13">
+        <v>1.73</v>
+      </c>
+      <c r="AR13">
+        <v>2.27</v>
+      </c>
+      <c r="AS13">
+        <v>2.97</v>
+      </c>
+      <c r="AT13">
+        <v>3.95</v>
+      </c>
+      <c r="AU13">
+        <v>2.57</v>
+      </c>
+      <c r="AV13">
+        <v>1.95</v>
+      </c>
+      <c r="AW13">
+        <v>1.53</v>
+      </c>
+      <c r="AX13">
         <v>1.3</v>
       </c>
-      <c r="AR13">
-        <v>1.65</v>
-      </c>
-      <c r="AS13">
-        <v>2</v>
-      </c>
-      <c r="AT13">
-        <v>2.4</v>
-      </c>
-      <c r="AU13">
-        <v>3.55</v>
-      </c>
-      <c r="AV13">
-        <v>2.97</v>
-      </c>
-      <c r="AW13">
-        <v>2.2</v>
-      </c>
-      <c r="AX13">
-        <v>1.78</v>
-      </c>
       <c r="AY13">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -2902,10 +2902,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BC13">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="BD13" s="3">
         <v>45838.79166666666</v>
@@ -2946,13 +2946,13 @@
         <v>105</v>
       </c>
       <c r="L14">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="M14">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="O14">
         <v>1.83</v>
@@ -2964,52 +2964,52 @@
         <v>2.5</v>
       </c>
       <c r="R14">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S14">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T14">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="U14">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V14">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y14">
-        <v>6.55</v>
+        <v>6.9</v>
       </c>
       <c r="Z14">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AA14">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AB14">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AC14">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AD14">
         <v>4.7</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG14">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH14">
         <v>10</v>
@@ -3024,46 +3024,46 @@
         <v>106</v>
       </c>
       <c r="AL14">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AM14">
         <v>1.37</v>
       </c>
       <c r="AN14">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AQ14">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AS14">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AT14">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AU14">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AV14">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AW14">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="AX14">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AY14">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>74</v>
@@ -3134,28 +3134,28 @@
         <v>3.5</v>
       </c>
       <c r="R15">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S15">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="T15">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
         <v>1.32</v>
       </c>
       <c r="V15">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z15">
         <v>1.35</v>
@@ -3170,22 +3170,22 @@
         <v>1.57</v>
       </c>
       <c r="AD15">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AE15">
         <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AG15">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH15">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AI15">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AJ15" t="s">
         <v>106</v>
@@ -3194,7 +3194,7 @@
         <v>106</v>
       </c>
       <c r="AL15">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AM15">
         <v>1.27</v>
@@ -3206,31 +3206,31 @@
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AR15">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AS15">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AT15">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AU15">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="AV15">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="AW15">
         <v>2</v>
       </c>
       <c r="AX15">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AY15">
         <v>1.34</v>
@@ -3334,10 +3334,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD16">
         <v>0</v>

--- a/jogos_2025-06-30.xlsx
+++ b/jogos_2025-06-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="107">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -220,24 +166,21 @@
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
+    <t>Brazil Serie C</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
@@ -256,27 +199,24 @@
     <t>AGMK</t>
   </si>
   <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
     <t>Brann</t>
   </si>
   <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Mjällby</t>
+    <t>Floresta</t>
   </si>
   <si>
     <t>Philadelphia Union II</t>
   </si>
   <si>
-    <t>Floresta</t>
-  </si>
-  <si>
     <t>Paysandu</t>
   </si>
   <si>
-    <t>Colón</t>
-  </si>
-  <si>
     <t>Itabaiana</t>
   </si>
   <si>
@@ -301,27 +241,24 @@
     <t>Termez Surkhon</t>
   </si>
   <si>
+    <t>Malmö FF</t>
+  </si>
+  <si>
     <t>Sandefjord</t>
   </si>
   <si>
     <t>Norrköping</t>
   </si>
   <si>
-    <t>Malmö FF</t>
+    <t>Brusque</t>
   </si>
   <si>
     <t>Orlando City II</t>
   </si>
   <si>
-    <t>Brusque</t>
-  </si>
-  <si>
     <t>Ferroviária</t>
   </si>
   <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
@@ -331,10 +268,73 @@
     <t>Crown Legacy</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>incomplete</t>
   </si>
   <si>
+    <t>['50', '85']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['55', '83']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
+    <t>['4502']</t>
+  </si>
+  <si>
+    <t>['56', '72']</t>
+  </si>
+  <si>
+    <t>['65', '68']</t>
+  </si>
+  <si>
+    <t>['60']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['6', '32']</t>
+  </si>
+  <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['63', '77']</t>
+  </si>
+  <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['59']</t>
+  </si>
+  <si>
+    <t>['25']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
+    <t>['67']</t>
   </si>
 </sst>
 </file>
@@ -698,10 +698,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD16"/>
+  <dimension ref="A1:AL15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,94 +816,40 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45838</v>
       </c>
       <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" t="s">
-        <v>75</v>
-      </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L2">
         <v>2.67</v>
@@ -978,102 +924,48 @@
         <v>1.25</v>
       </c>
       <c r="AJ2" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="AK2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL2">
-        <v>1.54</v>
-      </c>
-      <c r="AM2">
-        <v>1.24</v>
-      </c>
-      <c r="AN2">
-        <v>1.5</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>1.15</v>
-      </c>
-      <c r="AQ2">
-        <v>1.29</v>
-      </c>
-      <c r="AR2">
-        <v>1.49</v>
-      </c>
-      <c r="AS2">
-        <v>1.77</v>
-      </c>
-      <c r="AT2">
-        <v>2.18</v>
-      </c>
-      <c r="AU2">
-        <v>4.4</v>
-      </c>
-      <c r="AV2">
-        <v>3.15</v>
-      </c>
-      <c r="AW2">
-        <v>2.4</v>
-      </c>
-      <c r="AX2">
-        <v>1.92</v>
-      </c>
-      <c r="AY2">
-        <v>1.58</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>2</v>
-      </c>
-      <c r="BC2">
-        <v>1.8</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>98</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45838.33333333334</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45838</v>
       </c>
       <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" t="s">
-        <v>76</v>
-      </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L3">
         <v>2.45</v>
@@ -1148,102 +1040,48 @@
         <v>1.1</v>
       </c>
       <c r="AJ3" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="AK3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL3">
-        <v>1.5</v>
-      </c>
-      <c r="AM3">
-        <v>1.28</v>
-      </c>
-      <c r="AN3">
-        <v>1.49</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>1.25</v>
-      </c>
-      <c r="AQ3">
-        <v>1.44</v>
-      </c>
-      <c r="AR3">
-        <v>1.72</v>
-      </c>
-      <c r="AS3">
-        <v>2.12</v>
-      </c>
-      <c r="AT3">
-        <v>2.65</v>
-      </c>
-      <c r="AU3">
-        <v>3.45</v>
-      </c>
-      <c r="AV3">
-        <v>2.55</v>
-      </c>
-      <c r="AW3">
-        <v>1.98</v>
-      </c>
-      <c r="AX3">
-        <v>1.63</v>
-      </c>
-      <c r="AY3">
-        <v>1.41</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.91</v>
-      </c>
-      <c r="BC3">
-        <v>1.91</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45838.35763888889</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45838</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L4">
         <v>1.35</v>
@@ -1318,102 +1156,48 @@
         <v>1.22</v>
       </c>
       <c r="AJ4" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="AK4" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL4">
-        <v>1.09</v>
-      </c>
-      <c r="AM4">
-        <v>1.17</v>
-      </c>
-      <c r="AN4">
-        <v>2.86</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>1.25</v>
-      </c>
-      <c r="AQ4">
-        <v>1.43</v>
-      </c>
-      <c r="AR4">
-        <v>1.71</v>
-      </c>
-      <c r="AS4">
-        <v>2.08</v>
-      </c>
-      <c r="AT4">
-        <v>2.63</v>
-      </c>
-      <c r="AU4">
-        <v>3.45</v>
-      </c>
-      <c r="AV4">
-        <v>2.55</v>
-      </c>
-      <c r="AW4">
-        <v>2</v>
-      </c>
-      <c r="AX4">
-        <v>1.65</v>
-      </c>
-      <c r="AY4">
-        <v>1.41</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.29</v>
-      </c>
-      <c r="BC4">
-        <v>3.6</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>99</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45838.35763888889</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45838</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L5">
         <v>3.25</v>
@@ -1488,93 +1272,39 @@
         <v>1.11</v>
       </c>
       <c r="AJ5" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="AK5" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL5">
-        <v>1.73</v>
-      </c>
-      <c r="AM5">
-        <v>1.26</v>
-      </c>
-      <c r="AN5">
-        <v>1.33</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>1.27</v>
-      </c>
-      <c r="AQ5">
-        <v>1.48</v>
-      </c>
-      <c r="AR5">
-        <v>1.77</v>
-      </c>
-      <c r="AS5">
-        <v>2.18</v>
-      </c>
-      <c r="AT5">
-        <v>2.8</v>
-      </c>
-      <c r="AU5">
-        <v>3.3</v>
-      </c>
-      <c r="AV5">
-        <v>2.45</v>
-      </c>
-      <c r="AW5">
-        <v>1.92</v>
-      </c>
-      <c r="AX5">
-        <v>1.58</v>
-      </c>
-      <c r="AY5">
-        <v>1.37</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>2.3</v>
-      </c>
-      <c r="BC5">
-        <v>1.67</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45838.375</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45838</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s">
         <v>74</v>
       </c>
-      <c r="E6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" t="s">
-        <v>94</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1583,335 +1313,227 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L6">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M6">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N6">
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>1.27</v>
+      </c>
+      <c r="S6">
+        <v>3.28</v>
+      </c>
+      <c r="T6">
+        <v>2.35</v>
+      </c>
+      <c r="U6">
+        <v>1.52</v>
+      </c>
+      <c r="V6">
         <v>5.5</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>1.35</v>
-      </c>
-      <c r="S6">
-        <v>2.85</v>
-      </c>
-      <c r="T6">
-        <v>2.45</v>
-      </c>
-      <c r="U6">
-        <v>1.45</v>
-      </c>
-      <c r="V6">
-        <v>6.5</v>
-      </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>9.199999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="Z6">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AA6">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC6">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD6">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="AE6">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AF6">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH6">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI6">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AJ6" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL6">
-        <v>1.12</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>2.45</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>0</v>
-      </c>
-      <c r="BC6">
-        <v>0</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>101</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45838.5</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45838</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L7">
-        <v>1.46</v>
+        <v>2.56</v>
       </c>
       <c r="M7">
-        <v>4.2</v>
+        <v>3.13</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>2.44</v>
       </c>
       <c r="O7">
+        <v>2.1</v>
+      </c>
+      <c r="P7">
+        <v>9</v>
+      </c>
+      <c r="Q7">
+        <v>1.83</v>
+      </c>
+      <c r="R7">
         <v>1.36</v>
       </c>
-      <c r="P7">
-        <v>16</v>
-      </c>
-      <c r="Q7">
+      <c r="S7">
         <v>3</v>
       </c>
-      <c r="R7">
-        <v>1.22</v>
-      </c>
-      <c r="S7">
-        <v>4</v>
-      </c>
       <c r="T7">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V7">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AA7">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB7">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="AC7">
-        <v>2.78</v>
+        <v>1.82</v>
       </c>
       <c r="AD7">
-        <v>2.01</v>
+        <v>3.4</v>
       </c>
       <c r="AE7">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AF7">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AH7">
-        <v>3.55</v>
+        <v>6.5</v>
       </c>
       <c r="AI7">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AJ7" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="AK7" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL7">
-        <v>1.16</v>
-      </c>
-      <c r="AM7">
-        <v>1.19</v>
-      </c>
-      <c r="AN7">
-        <v>2.4</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>1.19</v>
-      </c>
-      <c r="AQ7">
-        <v>1.33</v>
-      </c>
-      <c r="AR7">
-        <v>1.54</v>
-      </c>
-      <c r="AS7">
-        <v>1.85</v>
-      </c>
-      <c r="AT7">
-        <v>2.32</v>
-      </c>
-      <c r="AU7">
-        <v>4.1</v>
-      </c>
-      <c r="AV7">
-        <v>2.95</v>
-      </c>
-      <c r="AW7">
-        <v>2.3</v>
-      </c>
-      <c r="AX7">
-        <v>1.83</v>
-      </c>
-      <c r="AY7">
-        <v>1.53</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.36</v>
-      </c>
-      <c r="BC7">
-        <v>3</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>102</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45838.58333333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45838</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1923,502 +1545,340 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L8">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="M8">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N8">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="Q8">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S8">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T8">
+        <v>2.1</v>
+      </c>
+      <c r="U8">
+        <v>1.67</v>
+      </c>
+      <c r="V8">
+        <v>4.5</v>
+      </c>
+      <c r="W8">
+        <v>1.18</v>
+      </c>
+      <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
+        <v>17</v>
+      </c>
+      <c r="Z8">
+        <v>1.13</v>
+      </c>
+      <c r="AA8">
+        <v>5.75</v>
+      </c>
+      <c r="AB8">
+        <v>1.41</v>
+      </c>
+      <c r="AC8">
+        <v>2.78</v>
+      </c>
+      <c r="AD8">
+        <v>2.01</v>
+      </c>
+      <c r="AE8">
+        <v>1.71</v>
+      </c>
+      <c r="AF8">
+        <v>1.53</v>
+      </c>
+      <c r="AG8">
         <v>2.38</v>
       </c>
-      <c r="U8">
-        <v>1.53</v>
-      </c>
-      <c r="V8">
-        <v>6</v>
-      </c>
-      <c r="W8">
-        <v>1.13</v>
-      </c>
-      <c r="X8">
-        <v>1.04</v>
-      </c>
-      <c r="Y8">
-        <v>11</v>
-      </c>
-      <c r="Z8">
-        <v>1.22</v>
-      </c>
-      <c r="AA8">
-        <v>4.33</v>
-      </c>
-      <c r="AB8">
-        <v>1.65</v>
-      </c>
-      <c r="AC8">
-        <v>2.05</v>
-      </c>
-      <c r="AD8">
-        <v>2.27</v>
-      </c>
-      <c r="AE8">
-        <v>1.56</v>
-      </c>
-      <c r="AF8">
-        <v>1.67</v>
-      </c>
-      <c r="AG8">
-        <v>2.1</v>
-      </c>
       <c r="AH8">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="AI8">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AJ8" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AK8" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL8">
-        <v>1.21</v>
-      </c>
-      <c r="AM8">
-        <v>1.25</v>
-      </c>
-      <c r="AN8">
-        <v>2</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>1.18</v>
-      </c>
-      <c r="AQ8">
-        <v>1.3</v>
-      </c>
-      <c r="AR8">
-        <v>1.52</v>
-      </c>
-      <c r="AS8">
-        <v>1.81</v>
-      </c>
-      <c r="AT8">
-        <v>2.23</v>
-      </c>
-      <c r="AU8">
-        <v>4.2</v>
-      </c>
-      <c r="AV8">
-        <v>3.05</v>
-      </c>
-      <c r="AW8">
-        <v>2.33</v>
-      </c>
-      <c r="AX8">
-        <v>1.88</v>
-      </c>
-      <c r="AY8">
-        <v>1.56</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.44</v>
-      </c>
-      <c r="BC8">
-        <v>2.75</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45838.58333333334</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45838</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L9">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
       <c r="M9">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="N9">
-        <v>2.44</v>
+        <v>4.1</v>
       </c>
       <c r="O9">
+        <v>1.44</v>
+      </c>
+      <c r="P9">
+        <v>11.5</v>
+      </c>
+      <c r="Q9">
+        <v>2.75</v>
+      </c>
+      <c r="R9">
+        <v>1.3</v>
+      </c>
+      <c r="S9">
+        <v>3.4</v>
+      </c>
+      <c r="T9">
+        <v>2.38</v>
+      </c>
+      <c r="U9">
+        <v>1.53</v>
+      </c>
+      <c r="V9">
+        <v>6</v>
+      </c>
+      <c r="W9">
+        <v>1.13</v>
+      </c>
+      <c r="X9">
+        <v>1.04</v>
+      </c>
+      <c r="Y9">
+        <v>11</v>
+      </c>
+      <c r="Z9">
+        <v>1.22</v>
+      </c>
+      <c r="AA9">
+        <v>4.33</v>
+      </c>
+      <c r="AB9">
+        <v>1.65</v>
+      </c>
+      <c r="AC9">
+        <v>2.05</v>
+      </c>
+      <c r="AD9">
+        <v>2.27</v>
+      </c>
+      <c r="AE9">
+        <v>1.56</v>
+      </c>
+      <c r="AF9">
+        <v>1.67</v>
+      </c>
+      <c r="AG9">
         <v>2.1</v>
       </c>
-      <c r="P9">
-        <v>9</v>
-      </c>
-      <c r="Q9">
-        <v>1.83</v>
-      </c>
-      <c r="R9">
-        <v>1.36</v>
-      </c>
-      <c r="S9">
-        <v>3</v>
-      </c>
-      <c r="T9">
-        <v>2.75</v>
-      </c>
-      <c r="U9">
-        <v>1.4</v>
-      </c>
-      <c r="V9">
-        <v>8</v>
-      </c>
-      <c r="W9">
-        <v>1.08</v>
-      </c>
-      <c r="X9">
-        <v>1.06</v>
-      </c>
-      <c r="Y9">
-        <v>9</v>
-      </c>
-      <c r="Z9">
-        <v>1.33</v>
-      </c>
-      <c r="AA9">
-        <v>3.4</v>
-      </c>
-      <c r="AB9">
-        <v>1.88</v>
-      </c>
-      <c r="AC9">
-        <v>1.82</v>
-      </c>
-      <c r="AD9">
-        <v>3.4</v>
-      </c>
-      <c r="AE9">
-        <v>1.33</v>
-      </c>
-      <c r="AF9">
-        <v>1.7</v>
-      </c>
-      <c r="AG9">
-        <v>2.05</v>
-      </c>
       <c r="AH9">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AI9">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ9" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="AK9" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL9">
-        <v>1.49</v>
-      </c>
-      <c r="AM9">
-        <v>1.31</v>
-      </c>
-      <c r="AN9">
-        <v>1.44</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>1.23</v>
-      </c>
-      <c r="AQ9">
-        <v>1.38</v>
-      </c>
-      <c r="AR9">
-        <v>1.63</v>
-      </c>
-      <c r="AS9">
-        <v>1.97</v>
-      </c>
-      <c r="AT9">
-        <v>2.43</v>
-      </c>
-      <c r="AU9">
-        <v>3.7</v>
-      </c>
-      <c r="AV9">
-        <v>2.7</v>
-      </c>
-      <c r="AW9">
-        <v>2.12</v>
-      </c>
-      <c r="AX9">
-        <v>1.74</v>
-      </c>
-      <c r="AY9">
-        <v>1.48</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>2.1</v>
-      </c>
-      <c r="BC9">
-        <v>1.83</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>103</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45838.58333333334</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45838</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L10">
-        <v>1.38</v>
+        <v>2.65</v>
       </c>
       <c r="M10">
-        <v>4.5</v>
+        <v>2.66</v>
       </c>
       <c r="N10">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="O10">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
+        <v>1.57</v>
+      </c>
+      <c r="S10">
+        <v>2.2</v>
+      </c>
+      <c r="T10">
+        <v>3.7</v>
+      </c>
+      <c r="U10">
         <v>1.22</v>
       </c>
-      <c r="S10">
-        <v>3.8</v>
-      </c>
-      <c r="T10">
-        <v>2.04</v>
-      </c>
-      <c r="U10">
-        <v>1.78</v>
-      </c>
       <c r="V10">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="W10">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Z10">
-        <v>1.1</v>
+        <v>1.65</v>
       </c>
       <c r="AA10">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB10">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="AC10">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="AD10">
-        <v>1.98</v>
+        <v>6.25</v>
       </c>
       <c r="AE10">
-        <v>1.72</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>1.57</v>
+        <v>2.32</v>
       </c>
       <c r="AG10">
-        <v>2.32</v>
+        <v>1.58</v>
       </c>
       <c r="AH10">
-        <v>3.2</v>
+        <v>17</v>
       </c>
       <c r="AI10">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AJ10" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="AK10" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL10">
-        <v>1.15</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>2.85</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.3</v>
-      </c>
-      <c r="BC10">
-        <v>3.4</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>104</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45838.66666666666</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45838</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2433,186 +1893,132 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="L11">
-        <v>2.65</v>
+        <v>1.38</v>
       </c>
       <c r="M11">
-        <v>2.66</v>
+        <v>4.5</v>
       </c>
       <c r="N11">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="P11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R11">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="S11">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="T11">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="U11">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="V11">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>20</v>
+      </c>
+      <c r="Z11">
         <v>1.09</v>
       </c>
-      <c r="Y11">
-        <v>5.25</v>
-      </c>
-      <c r="Z11">
-        <v>1.65</v>
-      </c>
       <c r="AA11">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="AB11">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="AC11">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="AD11">
-        <v>5.8</v>
+        <v>1.96</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.75</v>
       </c>
       <c r="AF11">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AG11">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="AH11">
-        <v>11</v>
+        <v>3.1</v>
       </c>
       <c r="AI11">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AJ11" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="AK11" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL11">
-        <v>1.32</v>
-      </c>
-      <c r="AM11">
-        <v>1.43</v>
-      </c>
-      <c r="AN11">
-        <v>1.4</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>1.16</v>
-      </c>
-      <c r="AQ11">
-        <v>1.37</v>
-      </c>
-      <c r="AR11">
-        <v>1.93</v>
-      </c>
-      <c r="AS11">
-        <v>2.13</v>
-      </c>
-      <c r="AT11">
-        <v>2.3</v>
-      </c>
-      <c r="AU11">
-        <v>4.3</v>
-      </c>
-      <c r="AV11">
-        <v>2.66</v>
-      </c>
-      <c r="AW11">
-        <v>1.98</v>
-      </c>
-      <c r="AX11">
-        <v>1.6</v>
-      </c>
-      <c r="AY11">
-        <v>1.55</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>2</v>
-      </c>
-      <c r="BC11">
-        <v>2.4</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45838.66666666666</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45838</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L12">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="M12">
-        <v>2.87</v>
+        <v>3.24</v>
       </c>
       <c r="N12">
-        <v>3.84</v>
+        <v>4.25</v>
       </c>
       <c r="O12">
         <v>1.67</v>
@@ -2627,141 +2033,87 @@
         <v>1.55</v>
       </c>
       <c r="S12">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="T12">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U12">
         <v>1.27</v>
       </c>
       <c r="V12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>1</v>
       </c>
       <c r="X12">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z12">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AA12">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AB12">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="AC12">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AD12">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AE12">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF12">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG12">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH12">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AI12">
         <v>1.01</v>
       </c>
       <c r="AJ12" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="AK12" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL12">
-        <v>1.35</v>
-      </c>
-      <c r="AM12">
-        <v>1.3</v>
-      </c>
-      <c r="AN12">
-        <v>1.65</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>1.25</v>
-      </c>
-      <c r="AQ12">
-        <v>1.34</v>
-      </c>
-      <c r="AR12">
-        <v>1.6</v>
-      </c>
-      <c r="AS12">
-        <v>2.1</v>
-      </c>
-      <c r="AT12">
-        <v>2.37</v>
-      </c>
-      <c r="AU12">
-        <v>4.1</v>
-      </c>
-      <c r="AV12">
-        <v>2.97</v>
-      </c>
-      <c r="AW12">
-        <v>1.98</v>
-      </c>
-      <c r="AX12">
-        <v>1.78</v>
-      </c>
-      <c r="AY12">
-        <v>1.44</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.67</v>
-      </c>
-      <c r="BC12">
-        <v>2.88</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>105</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45838.79166666666</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45838</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2773,168 +2125,114 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L13">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="M13">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="N13">
-        <v>3.97</v>
+        <v>3.19</v>
       </c>
       <c r="O13">
+        <v>1.83</v>
+      </c>
+      <c r="P13">
+        <v>6</v>
+      </c>
+      <c r="Q13">
+        <v>2.5</v>
+      </c>
+      <c r="R13">
+        <v>1.47</v>
+      </c>
+      <c r="S13">
+        <v>2.4</v>
+      </c>
+      <c r="T13">
+        <v>3.5</v>
+      </c>
+      <c r="U13">
+        <v>1.25</v>
+      </c>
+      <c r="V13">
+        <v>11</v>
+      </c>
+      <c r="W13">
+        <v>1.04</v>
+      </c>
+      <c r="X13">
+        <v>1.11</v>
+      </c>
+      <c r="Y13">
+        <v>6</v>
+      </c>
+      <c r="Z13">
+        <v>1.53</v>
+      </c>
+      <c r="AA13">
+        <v>2.4</v>
+      </c>
+      <c r="AB13">
+        <v>2.62</v>
+      </c>
+      <c r="AC13">
+        <v>1.47</v>
+      </c>
+      <c r="AD13">
+        <v>5.15</v>
+      </c>
+      <c r="AE13">
+        <v>1.16</v>
+      </c>
+      <c r="AF13">
+        <v>2.1</v>
+      </c>
+      <c r="AG13">
         <v>1.73</v>
       </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>3.1</v>
-      </c>
-      <c r="R13">
-        <v>1.75</v>
-      </c>
-      <c r="S13">
-        <v>2.01</v>
-      </c>
-      <c r="T13">
-        <v>4</v>
-      </c>
-      <c r="U13">
-        <v>1.14</v>
-      </c>
-      <c r="V13">
-        <v>8.5</v>
-      </c>
-      <c r="W13">
-        <v>1.02</v>
-      </c>
-      <c r="X13">
-        <v>1.13</v>
-      </c>
-      <c r="Y13">
-        <v>4.4</v>
-      </c>
-      <c r="Z13">
-        <v>1.76</v>
-      </c>
-      <c r="AA13">
-        <v>1.94</v>
-      </c>
-      <c r="AB13">
-        <v>3.21</v>
-      </c>
-      <c r="AC13">
-        <v>1.3</v>
-      </c>
-      <c r="AD13">
-        <v>6.5</v>
-      </c>
-      <c r="AE13">
-        <v>1.1</v>
-      </c>
-      <c r="AF13">
-        <v>2.63</v>
-      </c>
-      <c r="AG13">
-        <v>1.44</v>
-      </c>
       <c r="AH13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AI13">
         <v>1</v>
       </c>
       <c r="AJ13" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="AK13" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL13">
-        <v>1.44</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>1.67</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>1.41</v>
-      </c>
-      <c r="AQ13">
-        <v>1.73</v>
-      </c>
-      <c r="AR13">
-        <v>2.27</v>
-      </c>
-      <c r="AS13">
-        <v>2.97</v>
-      </c>
-      <c r="AT13">
-        <v>3.95</v>
-      </c>
-      <c r="AU13">
-        <v>2.57</v>
-      </c>
-      <c r="AV13">
-        <v>1.95</v>
-      </c>
-      <c r="AW13">
-        <v>1.53</v>
-      </c>
-      <c r="AX13">
-        <v>1.3</v>
-      </c>
-      <c r="AY13">
-        <v>1.19</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.73</v>
-      </c>
-      <c r="BC13">
-        <v>3.1</v>
-      </c>
-      <c r="BD13" s="3">
-        <v>45838.79166666666</v>
+        <v>90</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>45838.8125</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45838</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2943,168 +2241,114 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L14">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="M14">
-        <v>2.99</v>
+        <v>3.48</v>
       </c>
       <c r="N14">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="O14">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="P14">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="Q14">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R14">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S14">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T14">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="U14">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V14">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
         <v>1.1</v>
       </c>
       <c r="Y14">
-        <v>6.9</v>
+        <v>7.38</v>
       </c>
       <c r="Z14">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AA14">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AB14">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AC14">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AD14">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AE14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF14">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG14">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AH14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI14">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ14" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="AK14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL14">
-        <v>1.27</v>
-      </c>
-      <c r="AM14">
-        <v>1.37</v>
-      </c>
-      <c r="AN14">
-        <v>1.57</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>1.14</v>
-      </c>
-      <c r="AQ14">
-        <v>1.36</v>
-      </c>
-      <c r="AR14">
-        <v>1.52</v>
-      </c>
-      <c r="AS14">
-        <v>1.95</v>
-      </c>
-      <c r="AT14">
-        <v>2.4</v>
-      </c>
-      <c r="AU14">
-        <v>3.8</v>
-      </c>
-      <c r="AV14">
-        <v>2.88</v>
-      </c>
-      <c r="AW14">
-        <v>2.2</v>
-      </c>
-      <c r="AX14">
-        <v>1.74</v>
-      </c>
-      <c r="AY14">
-        <v>1.45</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.83</v>
-      </c>
-      <c r="BC14">
-        <v>2.5</v>
-      </c>
-      <c r="BD14" s="3">
-        <v>45838.8125</v>
+        <v>91</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>45838.875</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45838</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -3113,311 +2357,87 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L15">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="M15">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N15">
-        <v>5.3</v>
+        <v>3.75</v>
       </c>
       <c r="O15">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="P15">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
         <v>1.5</v>
       </c>
-      <c r="S15">
-        <v>2.35</v>
-      </c>
-      <c r="T15">
-        <v>3.1</v>
-      </c>
-      <c r="U15">
-        <v>1.32</v>
-      </c>
-      <c r="V15">
-        <v>8</v>
-      </c>
-      <c r="W15">
-        <v>1.05</v>
-      </c>
-      <c r="X15">
-        <v>1.08</v>
-      </c>
-      <c r="Y15">
-        <v>7.8</v>
-      </c>
-      <c r="Z15">
-        <v>1.35</v>
-      </c>
-      <c r="AA15">
-        <v>3</v>
-      </c>
-      <c r="AB15">
+      <c r="AC15">
+        <v>2.5</v>
+      </c>
+      <c r="AD15">
         <v>2.15</v>
       </c>
-      <c r="AC15">
-        <v>1.57</v>
-      </c>
-      <c r="AD15">
-        <v>3.8</v>
-      </c>
       <c r="AE15">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AF15">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s">
         <v>106</v>
       </c>
-      <c r="AL15">
-        <v>1.14</v>
-      </c>
-      <c r="AM15">
-        <v>1.27</v>
-      </c>
-      <c r="AN15">
-        <v>2.2</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>1.25</v>
-      </c>
-      <c r="AQ15">
-        <v>1.34</v>
-      </c>
-      <c r="AR15">
-        <v>1.77</v>
-      </c>
-      <c r="AS15">
-        <v>2.1</v>
-      </c>
-      <c r="AT15">
-        <v>2.62</v>
-      </c>
-      <c r="AU15">
-        <v>3.6</v>
-      </c>
-      <c r="AV15">
-        <v>2.55</v>
-      </c>
-      <c r="AW15">
-        <v>2</v>
-      </c>
-      <c r="AX15">
-        <v>1.64</v>
-      </c>
-      <c r="AY15">
-        <v>1.34</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.44</v>
-      </c>
-      <c r="BC15">
-        <v>3.5</v>
-      </c>
-      <c r="BD15" s="3">
-        <v>45838.875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:56">
-      <c r="A16" s="2">
-        <v>45838</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" t="s">
-        <v>105</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>1.61</v>
-      </c>
-      <c r="AC16">
-        <v>2.25</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>106</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>0</v>
-      </c>
-      <c r="BC16">
-        <v>0</v>
-      </c>
-      <c r="BD16" s="3">
+      <c r="AL15" s="3">
         <v>45838.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-06-30.xlsx
+++ b/jogos_2025-06-30.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="N3" t="n">
-        <v>6.3</v>
+        <v>2.48</v>
       </c>
       <c r="O3" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.73</v>
+        <v>1.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['55', '83']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.86</v>
+        <v>1.49</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.6</v>
+        <v>1.91</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45838.35763888889</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>2.48</v>
+        <v>6.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['55', '83']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.49</v>
+        <v>2.86</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45838.35763888889</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>13</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>1.14</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>7.2</v>
+        <v>2.05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.53</v>
+        <v>4.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="U6" t="n">
-        <v>1.87</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>2.51</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['13', '17', '54', '56', '59', '65', '75']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45838.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.56</v>
+        <v>13</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>6.5</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>1.14</v>
       </c>
       <c r="O7" t="n">
-        <v>2.05</v>
+        <v>7.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.31</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.4</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.51</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['13', '17', '54', '56', '59', '65', '75']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45838.5</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q8" t="n">
         <v>4</v>
       </c>
-      <c r="N8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="O8" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.02</v>
-      </c>
       <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.44</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.36</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['73', '90+3']</t>
+          <t>['39', '62']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.2</v>
+        <v>1.61</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45838.54166666666</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>2.45</v>
+        <v>1.88</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['48', '88']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.33</v>
       </c>
-      <c r="S9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['39', '62']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45838.54166666666</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,20 +1675,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.36</v>
       </c>
-      <c r="M10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.6</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['73', '90+3']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.18</v>
       </c>
-      <c r="X10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['48', '88']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH10" t="n">
-        <v>2.85</v>
+        <v>1.04</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3.5</v>
+        <v>1.44</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45838.54166666666</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1819,10 +1819,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>2.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.13</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X11" t="n">
         <v>3.4</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.33</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="Z11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD11" t="n">
         <v>2.05</v>
       </c>
-      <c r="AA11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI11" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['4502']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45838.58333333334</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2077,10 +2077,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>2.44</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['4502']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>2.75</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['8']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45838.58333333334</v>
